--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T14:06:36+00:00</t>
+    <t>2026-09-07T14:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T14:36:51+00:00</t>
+    <t>2026-09-07T15:01:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:01:48+00:00</t>
+    <t>2026-09-07T15:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:24:11+00:00</t>
+    <t>2026-09-07T16:10:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:10:41+00:00</t>
+    <t>2026-09-08T07:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T07:03:30+00:00</t>
+    <t>2026-09-08T09:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:54:25+00:00</t>
+    <t>2026-09-08T10:20:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:20:08+00:00</t>
+    <t>2026-09-08T10:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:47:56+00:00</t>
+    <t>2026-09-08T11:13:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:13:58+00:00</t>
+    <t>2026-09-08T15:05:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:05:20+00:00</t>
+    <t>2026-09-08T15:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:29:28+00:00</t>
+    <t>2026-09-08T15:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:57:39+00:00</t>
+    <t>2026-09-08T16:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T16:46:13+00:00</t>
+    <t>2026-09-10T06:46:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T06:46:47+00:00</t>
+    <t>2026-09-10T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:44:28+00:00</t>
+    <t>2026-09-10T15:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T15:13:00+00:00</t>
+    <t>2026-09-10T16:21:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:21:19+00:00</t>
+    <t>2026-09-10T16:43:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot.rc5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:43:20+00:00</t>
+    <t>2026-09-11T09:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:22:31+00:00</t>
+    <t>2026-09-11T11:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc5</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:18+00:00</t>
+    <t>2026-09-11T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:40:31+00:00</t>
+    <t>2026-09-11T14:12:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:12:49+00:00</t>
+    <t>2026-09-11T14:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
+++ b/branches/dev/ValueSet-mii-vs-pro-bdi-bdi2-short.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:35:48+00:00</t>
+    <t>2026-09-11T15:01:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
